--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_231_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_231_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1727,7 +1727,7 @@
         <v>19</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>14</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>82</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>27</v>
@@ -4491,13 +4491,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>4</v>
@@ -4883,13 +4883,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>7</v>
@@ -5468,16 +5468,16 @@
         <v>7</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>2</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6448,7 +6448,7 @@
         <v>8</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>97</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>28</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_231_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_231_EL.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
         <v>8</v>
@@ -854,17 +854,17 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>87.50</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,10 +1739,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2131,14 +2131,14 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA21" t="n">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>1</v>
       </c>
       <c r="X30" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4500,10 +4500,10 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -4928,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
@@ -4939,11 +4939,11 @@
         <v>1</v>
       </c>
       <c r="AK38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5480,10 +5480,10 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y43" t="n">
         <v>6</v>
       </c>
-      <c r="Y43" t="n">
-        <v>8</v>
-      </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,14 +6264,14 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6460,10 +6460,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="Y48" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -6843,11 +6843,11 @@
         <v>7</v>
       </c>
       <c r="AK48" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
